--- a/data/output/sim_gridrnd/REL1/group_500_40/results/REL1_G5_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_500_40/results/REL1_G5_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,860 +466,981 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G5_501_41_REL1</t>
+          <t>S01_G5_499_41_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C2" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D2" t="n">
         <v>41</v>
       </c>
-      <c r="D2" t="n">
-        <v>60.78576723498888</v>
-      </c>
       <c r="E2" t="n">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>514.8307854719644</v>
-      </c>
-      <c r="J2" t="n">
-        <v>64.24314294655969</v>
-      </c>
-      <c r="K2" t="n">
-        <v>504.3401306219749</v>
-      </c>
-      <c r="L2" t="n">
-        <v>51.66445938811344</v>
-      </c>
-      <c r="M2" t="n">
-        <v>509.6683897585373</v>
-      </c>
-      <c r="N2" t="n">
-        <v>49.80186467072558</v>
-      </c>
-      <c r="O2" t="n">
-        <v>506.8713092567463</v>
-      </c>
-      <c r="P2" t="n">
-        <v>46.40961687602459</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>509.8546253669325</v>
-      </c>
       <c r="R2" t="n">
-        <v>45.1907333944395</v>
+        <v>523.36</v>
       </c>
       <c r="S2" t="n">
-        <v>507.897052592993</v>
+        <v>50.79</v>
       </c>
       <c r="T2" t="n">
-        <v>46.17133534040364</v>
+        <v>515.23</v>
       </c>
       <c r="U2" t="n">
-        <v>507.4065980296538</v>
+        <v>44.78</v>
       </c>
       <c r="V2" t="n">
-        <v>43.8494427569554</v>
+        <v>510.2</v>
       </c>
       <c r="W2" t="n">
-        <v>507.0197174907497</v>
+        <v>47.61</v>
       </c>
       <c r="X2" t="n">
-        <v>42.51302777244815</v>
+        <v>505.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>503.0497462328718</v>
+        <v>53.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.75907679311054</v>
+        <v>506.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>49.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>500.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>47.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>502.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>45.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>508.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>44.63</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>504.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>43.64</v>
       </c>
       <c r="AJ2" t="n">
-        <v>498.625</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>498.9333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>498.525</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>498.82</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>497.9583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>498.2785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>499.225</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>498.6888888888889</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>498.46</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>78.35741429501104</v>
+        <v>499.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.60716379067689</v>
+        <v>500.0166666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>69.67459633898139</v>
+        <v>500.0375</v>
       </c>
       <c r="AV2" t="n">
-        <v>63.85270237037741</v>
+        <v>500.16</v>
       </c>
       <c r="AW2" t="n">
-        <v>59.72065469519086</v>
+        <v>500.0083333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>55.87320695200913</v>
+        <v>500.3357142857143</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.90001707650008</v>
+        <v>499.45</v>
       </c>
       <c r="AZ2" t="n">
-        <v>53.51357967727952</v>
+        <v>499.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>53.4026066779516</v>
+        <v>499.605</v>
       </c>
       <c r="BB2" t="n">
-        <v>373</v>
+        <v>74.86681507851125</v>
       </c>
       <c r="BC2" t="n">
-        <v>373</v>
+        <v>69.72314098553571</v>
       </c>
       <c r="BD2" t="n">
-        <v>373</v>
+        <v>64.20970404658473</v>
       </c>
       <c r="BE2" t="n">
-        <v>373</v>
+        <v>61.39637122827374</v>
       </c>
       <c r="BF2" t="n">
-        <v>373</v>
+        <v>58.09611229582311</v>
       </c>
       <c r="BG2" t="n">
-        <v>373</v>
+        <v>54.9002485961436</v>
       </c>
       <c r="BH2" t="n">
-        <v>373</v>
+        <v>53.39777617092307</v>
       </c>
       <c r="BI2" t="n">
-        <v>373</v>
+        <v>52.14579987347442</v>
       </c>
       <c r="BJ2" t="n">
-        <v>373</v>
+        <v>51.02968719284883</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.8333333333333334</v>
+        <v>636</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.8333333333333334</v>
+        <v>636</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.8333333333333334</v>
+        <v>636</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.8333333333333334</v>
+        <v>636</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.8181818181818182</v>
+        <v>636</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.9565217391304348</v>
+        <v>636</v>
       </c>
       <c r="CB2" t="n">
-        <v>1</v>
+        <v>636</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>504.9</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>43.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G5_499_41_REL1</t>
+          <t>S02_G5_501_41_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C3" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D3" t="n">
         <v>41</v>
       </c>
-      <c r="D3" t="n">
-        <v>60.78576723498888</v>
-      </c>
       <c r="E3" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>523.3601312103552</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50.79336425694486</v>
-      </c>
-      <c r="K3" t="n">
-        <v>515.2289926834485</v>
-      </c>
-      <c r="L3" t="n">
-        <v>44.77617542988168</v>
-      </c>
-      <c r="M3" t="n">
-        <v>510.2049509316535</v>
-      </c>
-      <c r="N3" t="n">
-        <v>47.60982193089057</v>
-      </c>
-      <c r="O3" t="n">
-        <v>505.582750139676</v>
-      </c>
-      <c r="P3" t="n">
-        <v>53.32737967862276</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>506.2820585876149</v>
-      </c>
       <c r="R3" t="n">
-        <v>49.29261862581978</v>
+        <v>514.83</v>
       </c>
       <c r="S3" t="n">
-        <v>500.5542757352299</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>47.63999164455791</v>
+        <v>504.34</v>
       </c>
       <c r="U3" t="n">
-        <v>502.4455881177637</v>
+        <v>51.66</v>
       </c>
       <c r="V3" t="n">
-        <v>45.42000739219567</v>
+        <v>509.67</v>
       </c>
       <c r="W3" t="n">
-        <v>508.7760907348504</v>
+        <v>49.8</v>
       </c>
       <c r="X3" t="n">
-        <v>44.63456224103889</v>
+        <v>506.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>504.8999692828251</v>
+        <v>46.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.63870370305304</v>
+        <v>509.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>45.19</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>507.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>46.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>507.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>43.85</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>507.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>42.51</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>503.05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>40.76</v>
       </c>
       <c r="AJ3" t="n">
-        <v>499.9</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>500.0166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>500.0375</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>500.16</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>500.0083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>500.3357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>499.45</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>499.4</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>499.605</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>74.86681507851125</v>
+        <v>498.625</v>
       </c>
       <c r="AT3" t="n">
-        <v>69.72314098553571</v>
+        <v>498.9333333333333</v>
       </c>
       <c r="AU3" t="n">
-        <v>64.20970404658473</v>
+        <v>498.525</v>
       </c>
       <c r="AV3" t="n">
-        <v>61.39637122827374</v>
+        <v>498.82</v>
       </c>
       <c r="AW3" t="n">
-        <v>58.09611229582311</v>
+        <v>497.9583333333333</v>
       </c>
       <c r="AX3" t="n">
-        <v>54.9002485961436</v>
+        <v>498.2785714285714</v>
       </c>
       <c r="AY3" t="n">
-        <v>53.39777617092307</v>
+        <v>499.225</v>
       </c>
       <c r="AZ3" t="n">
-        <v>52.14579987347442</v>
+        <v>498.6888888888889</v>
       </c>
       <c r="BA3" t="n">
-        <v>51.02968719284883</v>
+        <v>498.46</v>
       </c>
       <c r="BB3" t="n">
-        <v>336</v>
+        <v>78.35741429501104</v>
       </c>
       <c r="BC3" t="n">
-        <v>336</v>
+        <v>74.60716379067689</v>
       </c>
       <c r="BD3" t="n">
-        <v>336</v>
+        <v>69.67459633898139</v>
       </c>
       <c r="BE3" t="n">
-        <v>336</v>
+        <v>63.85270237037741</v>
       </c>
       <c r="BF3" t="n">
-        <v>336</v>
+        <v>59.72065469519086</v>
       </c>
       <c r="BG3" t="n">
-        <v>336</v>
+        <v>55.87320695200913</v>
       </c>
       <c r="BH3" t="n">
-        <v>336</v>
+        <v>54.90001707650008</v>
       </c>
       <c r="BI3" t="n">
-        <v>336</v>
+        <v>53.51357967727952</v>
       </c>
       <c r="BJ3" t="n">
-        <v>336</v>
+        <v>53.4026066779516</v>
       </c>
       <c r="BK3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BL3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BM3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BN3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BO3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BP3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BQ3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BR3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BS3" t="n">
-        <v>636</v>
+        <v>373</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.9333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.7894736842105263</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.7037037037037037</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>503.05</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>40.76</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>499</v>
       </c>
       <c r="C4" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D4" t="n">
         <v>38</v>
-      </c>
-      <c r="D4" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E4" t="n">
         <v>499</v>
@@ -1344,228 +1465,261 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>456.0020192690422</v>
-      </c>
-      <c r="J4" t="n">
-        <v>35.94604415521977</v>
-      </c>
-      <c r="K4" t="n">
-        <v>475.2094371817784</v>
-      </c>
-      <c r="L4" t="n">
-        <v>46.99507032697331</v>
-      </c>
-      <c r="M4" t="n">
-        <v>482.9988318193484</v>
-      </c>
-      <c r="N4" t="n">
-        <v>41.79299710108477</v>
-      </c>
-      <c r="O4" t="n">
-        <v>486.3240233698507</v>
-      </c>
-      <c r="P4" t="n">
-        <v>47.95858510542304</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>480.9670154407927</v>
-      </c>
       <c r="R4" t="n">
-        <v>50.31107839344358</v>
+        <v>456</v>
       </c>
       <c r="S4" t="n">
-        <v>485.7378377081834</v>
+        <v>35.95</v>
       </c>
       <c r="T4" t="n">
-        <v>53.49997351309438</v>
+        <v>475.21</v>
       </c>
       <c r="U4" t="n">
-        <v>487.1711288892268</v>
+        <v>47</v>
       </c>
       <c r="V4" t="n">
-        <v>55.86518842023889</v>
+        <v>483</v>
       </c>
       <c r="W4" t="n">
-        <v>492.2059923871054</v>
+        <v>41.79</v>
       </c>
       <c r="X4" t="n">
-        <v>63.72584746212043</v>
+        <v>486.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>493.2557635457597</v>
+        <v>47.96</v>
       </c>
       <c r="Z4" t="n">
-        <v>60.38640277258858</v>
+        <v>480.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>50.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>485.74</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>53.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>487.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>55.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>492.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>63.73</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>493.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>60.39</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>502.55</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>503.65</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>502.2625</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>501.44</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>500.525</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>500.6</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>500.36875</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>499.8111111111111</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>499.99</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>81.17602786537415</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>74.43113707761468</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>68.17747864031054</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>65.41472617079428</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>66.95221710294589</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>65.57458131231731</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>65.9398989492515</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>65.28065809248291</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>65.82788087125394</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>357</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>357</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>357</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>357</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>357</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>357</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>357</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>357</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>357</v>
       </c>
-      <c r="BK4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>669</v>
-      </c>
       <c r="BT4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>1</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.875</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.85</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.75</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.6842105263157895</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>493.26</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>60.39</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>501</v>
       </c>
       <c r="C5" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D5" t="n">
         <v>39</v>
-      </c>
-      <c r="D5" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E5" t="n">
         <v>501</v>
@@ -1590,720 +1744,819 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>478.9070437097156</v>
-      </c>
-      <c r="J5" t="n">
-        <v>46.11077725332887</v>
-      </c>
-      <c r="K5" t="n">
-        <v>489.6992497424752</v>
-      </c>
-      <c r="L5" t="n">
-        <v>55.54141387560039</v>
-      </c>
-      <c r="M5" t="n">
-        <v>484.6835643955069</v>
-      </c>
-      <c r="N5" t="n">
-        <v>52.46250232272456</v>
-      </c>
-      <c r="O5" t="n">
-        <v>489.8392692978204</v>
-      </c>
-      <c r="P5" t="n">
-        <v>49.06326437914787</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>492.5612210248738</v>
-      </c>
       <c r="R5" t="n">
-        <v>51.35416201871216</v>
+        <v>478.91</v>
       </c>
       <c r="S5" t="n">
-        <v>493.7520785755668</v>
+        <v>46.11</v>
       </c>
       <c r="T5" t="n">
-        <v>51.18807333991747</v>
+        <v>489.7</v>
       </c>
       <c r="U5" t="n">
-        <v>497.3304446588927</v>
+        <v>55.54</v>
       </c>
       <c r="V5" t="n">
-        <v>48.74923724970484</v>
+        <v>484.68</v>
       </c>
       <c r="W5" t="n">
-        <v>498.4743748038572</v>
+        <v>52.46</v>
       </c>
       <c r="X5" t="n">
-        <v>53.56812384803617</v>
+        <v>489.84</v>
       </c>
       <c r="Y5" t="n">
-        <v>498.3110285605925</v>
+        <v>49.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>52.56020902366987</v>
+        <v>492.56</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>51.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>493.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>51.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>497.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>48.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>498.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>53.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>498.31</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>52.56</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>502.85</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>503.7833333333334</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>502.1875</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>503.04</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>501.2666666666667</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>501.1285714285714</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>500.55625</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>501.2444444444445</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>500.75</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>88.8027448900089</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>78.43576813050423</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>76.32677999070837</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>72.76673965487254</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>69.14811799479594</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>67.63693442165444</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>65.03909851725729</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>65.83182464281596</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>66.48900285009545</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>333</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>333</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>333</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>333</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>333</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>333</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>333</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>333</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>333</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>678</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>678</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>678</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>678</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>678</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>678</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>678</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>678</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>678</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.88</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.8461538461538461</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>498.31</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>52.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G5_498_40_REL1</t>
+          <t>S05_G5_499_39_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D6" t="n">
-        <v>59.30318754633062</v>
+        <v>39</v>
       </c>
       <c r="E6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>512.7853530316183</v>
-      </c>
-      <c r="J6" t="n">
-        <v>45.18730338187756</v>
-      </c>
-      <c r="K6" t="n">
-        <v>518.436965934912</v>
-      </c>
-      <c r="L6" t="n">
-        <v>59.36257358732642</v>
-      </c>
-      <c r="M6" t="n">
-        <v>508.1461072534786</v>
-      </c>
-      <c r="N6" t="n">
-        <v>61.13311095239326</v>
-      </c>
-      <c r="O6" t="n">
-        <v>503.7451981762004</v>
-      </c>
-      <c r="P6" t="n">
-        <v>57.28971298748198</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>501.2955971698262</v>
-      </c>
       <c r="R6" t="n">
-        <v>53.02527806679617</v>
+        <v>479.5</v>
       </c>
       <c r="S6" t="n">
-        <v>495.1056156314447</v>
+        <v>34.03</v>
       </c>
       <c r="T6" t="n">
-        <v>51.59004774411788</v>
+        <v>486.76</v>
       </c>
       <c r="U6" t="n">
-        <v>494.1697660139094</v>
+        <v>37.28</v>
       </c>
       <c r="V6" t="n">
-        <v>50.93000293578568</v>
+        <v>488.58</v>
       </c>
       <c r="W6" t="n">
-        <v>496.0862678449752</v>
+        <v>38.89</v>
       </c>
       <c r="X6" t="n">
-        <v>50.91816846497094</v>
+        <v>490.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>495.6663761951874</v>
+        <v>44.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>47.95640323968434</v>
+        <v>488.26</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>46.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>489.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>52.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>491.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>48.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>492.36</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>47.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>490.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>49.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>494.625</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>495.9166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>497.375</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>497.93</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>498.7666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>499.9</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>501.23125</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>500.9444444444445</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>501.085</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>59.47465321462581</v>
+        <v>506.725</v>
       </c>
       <c r="AT6" t="n">
-        <v>61.70448164886855</v>
+        <v>505.8333333333333</v>
       </c>
       <c r="AU6" t="n">
-        <v>62.78044580122062</v>
+        <v>503.1625</v>
       </c>
       <c r="AV6" t="n">
-        <v>61.69299068775966</v>
+        <v>502.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>60.57347237492296</v>
+        <v>502.2583333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>59.05182953498199</v>
+        <v>501.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>58.32765444827608</v>
+        <v>500.75625</v>
       </c>
       <c r="AZ6" t="n">
-        <v>56.71475628306018</v>
+        <v>500.3222222222222</v>
       </c>
       <c r="BA6" t="n">
-        <v>56.46439386905698</v>
+        <v>501</v>
       </c>
       <c r="BB6" t="n">
-        <v>330</v>
+        <v>63.09872720586367</v>
       </c>
       <c r="BC6" t="n">
-        <v>330</v>
+        <v>55.21991387976704</v>
       </c>
       <c r="BD6" t="n">
-        <v>330</v>
+        <v>55.89665547910715</v>
       </c>
       <c r="BE6" t="n">
-        <v>330</v>
+        <v>57.39791895182263</v>
       </c>
       <c r="BF6" t="n">
-        <v>330</v>
+        <v>56.57848469653067</v>
       </c>
       <c r="BG6" t="n">
-        <v>330</v>
+        <v>57.79932340187284</v>
       </c>
       <c r="BH6" t="n">
-        <v>330</v>
+        <v>59.35568073855695</v>
       </c>
       <c r="BI6" t="n">
-        <v>330</v>
+        <v>57.13518623556626</v>
       </c>
       <c r="BJ6" t="n">
-        <v>330</v>
+        <v>58.12366127490593</v>
       </c>
       <c r="BK6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BL6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BM6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BN6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BO6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BP6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BQ6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BR6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BS6" t="n">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="BT6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CE6" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU6" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.9545454545454546</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.8214285714285714</v>
+      <c r="CF6" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>490.08</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>49.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G5_499_39_REL1</t>
+          <t>S06_G5_498_40_REL1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D7" t="n">
-        <v>57.82060785767235</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>479.5006032049579</v>
-      </c>
-      <c r="J7" t="n">
-        <v>34.02674046667585</v>
-      </c>
-      <c r="K7" t="n">
-        <v>486.7641847453692</v>
-      </c>
-      <c r="L7" t="n">
-        <v>37.28040159172102</v>
-      </c>
-      <c r="M7" t="n">
-        <v>488.5755310909441</v>
-      </c>
-      <c r="N7" t="n">
-        <v>38.88753091765893</v>
-      </c>
-      <c r="O7" t="n">
-        <v>490.0583032845403</v>
-      </c>
-      <c r="P7" t="n">
-        <v>44.72991187220379</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>488.2584733774955</v>
-      </c>
       <c r="R7" t="n">
-        <v>46.65634114888264</v>
+        <v>512.79</v>
       </c>
       <c r="S7" t="n">
-        <v>489.0854736667973</v>
+        <v>45.19</v>
       </c>
       <c r="T7" t="n">
-        <v>52.94870499490219</v>
+        <v>518.4400000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>491.3969950068974</v>
+        <v>59.36</v>
       </c>
       <c r="V7" t="n">
-        <v>48.56467747640662</v>
+        <v>508.15</v>
       </c>
       <c r="W7" t="n">
-        <v>492.3635754492988</v>
+        <v>61.13</v>
       </c>
       <c r="X7" t="n">
-        <v>47.29521276024849</v>
+        <v>503.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>490.0796447602239</v>
+        <v>57.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>49.04847999479662</v>
+        <v>501.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>53.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>495.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>51.59</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>494.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>50.93</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>496.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>50.92</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>495.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>47.96</v>
       </c>
       <c r="AJ7" t="n">
-        <v>506.725</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>505.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>503.1625</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>502.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>502.2583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>501.55</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>500.75625</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>500.3222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>63.09872720586367</v>
+        <v>494.625</v>
       </c>
       <c r="AT7" t="n">
-        <v>55.21991387976704</v>
+        <v>495.9166666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>55.89665547910715</v>
+        <v>497.375</v>
       </c>
       <c r="AV7" t="n">
-        <v>57.39791895182263</v>
+        <v>497.93</v>
       </c>
       <c r="AW7" t="n">
-        <v>56.57848469653067</v>
+        <v>498.7666666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>57.79932340187284</v>
+        <v>499.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>59.35568073855695</v>
+        <v>501.23125</v>
       </c>
       <c r="AZ7" t="n">
-        <v>57.13518623556626</v>
+        <v>500.9444444444445</v>
       </c>
       <c r="BA7" t="n">
-        <v>58.12366127490593</v>
+        <v>501.085</v>
       </c>
       <c r="BB7" t="n">
-        <v>388</v>
+        <v>59.47465321462581</v>
       </c>
       <c r="BC7" t="n">
-        <v>388</v>
+        <v>61.70448164886855</v>
       </c>
       <c r="BD7" t="n">
-        <v>388</v>
+        <v>62.78044580122062</v>
       </c>
       <c r="BE7" t="n">
-        <v>388</v>
+        <v>61.69299068775966</v>
       </c>
       <c r="BF7" t="n">
-        <v>388</v>
+        <v>60.57347237492296</v>
       </c>
       <c r="BG7" t="n">
-        <v>388</v>
+        <v>59.05182953498199</v>
       </c>
       <c r="BH7" t="n">
-        <v>388</v>
+        <v>58.32765444827608</v>
       </c>
       <c r="BI7" t="n">
-        <v>388</v>
+        <v>56.71475628306018</v>
       </c>
       <c r="BJ7" t="n">
-        <v>388</v>
+        <v>56.46439386905698</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BT7" t="n">
-        <v>1</v>
+        <v>610</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.9090909090909091</v>
+        <v>610</v>
       </c>
       <c r="BV7" t="n">
+        <v>610</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>610</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>610</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>610</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>610</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>610</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>610</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW7" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.92</v>
+      <c r="CD7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>495.67</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>47.96</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>499</v>
       </c>
       <c r="C8" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D8" t="n">
         <v>42</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E8" t="n">
         <v>499</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>499.6338598557969</v>
-      </c>
-      <c r="J8" t="n">
-        <v>50.49547600911254</v>
-      </c>
-      <c r="K8" t="n">
-        <v>495.8632291575331</v>
-      </c>
-      <c r="L8" t="n">
-        <v>47.28165821817966</v>
-      </c>
-      <c r="M8" t="n">
-        <v>500.7615776215187</v>
-      </c>
-      <c r="N8" t="n">
-        <v>43.98707393142178</v>
-      </c>
-      <c r="O8" t="n">
-        <v>498.4501259458804</v>
-      </c>
-      <c r="P8" t="n">
-        <v>39.73616968553969</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>496.3626060215175</v>
-      </c>
       <c r="R8" t="n">
-        <v>39.33876246301634</v>
+        <v>499.63</v>
       </c>
       <c r="S8" t="n">
-        <v>501.2672299207285</v>
+        <v>50.5</v>
       </c>
       <c r="T8" t="n">
-        <v>39.9055550903626</v>
+        <v>495.86</v>
       </c>
       <c r="U8" t="n">
-        <v>500.3399237462392</v>
+        <v>47.28</v>
       </c>
       <c r="V8" t="n">
-        <v>41.4603559962992</v>
+        <v>500.76</v>
       </c>
       <c r="W8" t="n">
-        <v>496.0465138613252</v>
+        <v>43.99</v>
       </c>
       <c r="X8" t="n">
-        <v>42.55455586730358</v>
+        <v>498.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>494.6081052487301</v>
+        <v>39.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>46.03661780283334</v>
+        <v>496.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>39.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>501.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>39.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>500.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>41.46</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>496.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>42.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>494.61</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>46.04</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>496.6</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>497.7833333333334</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>498.825</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>498.65</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>499.5916666666666</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>498.4428571428571</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>497.80625</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>497.0555555555555</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>497.87</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>67.66195385887109</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>63.14351158714216</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>59.35776591988617</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>57.52414710362945</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>53.36329822286309</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>50.7812214207141</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>50.80532660004756</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>51.09921963116052</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>53.33013313315465</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>333</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>333</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>333</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>333</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>333</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>333</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>333</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>333</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>333</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>613</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>613</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>613</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>613</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>613</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>613</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>613</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>613</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>613</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.5909090909090909</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.7096774193548387</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>494.61</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>46.04</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>501</v>
       </c>
       <c r="C9" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D9" t="n">
         <v>41</v>
-      </c>
-      <c r="D9" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E9" t="n">
         <v>501</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>486.9563845704477</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42.5591258153461</v>
-      </c>
-      <c r="K9" t="n">
-        <v>482.6606132028563</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60.1690687700256</v>
-      </c>
-      <c r="M9" t="n">
-        <v>477.6598777029326</v>
-      </c>
-      <c r="N9" t="n">
-        <v>59.09308060157766</v>
-      </c>
-      <c r="O9" t="n">
-        <v>486.9707762823941</v>
-      </c>
-      <c r="P9" t="n">
-        <v>58.42553674278522</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>490.1496686313699</v>
-      </c>
       <c r="R9" t="n">
-        <v>59.16385499371062</v>
+        <v>486.96</v>
       </c>
       <c r="S9" t="n">
-        <v>486.0160801403466</v>
+        <v>42.56</v>
       </c>
       <c r="T9" t="n">
-        <v>57.57196336499346</v>
+        <v>482.66</v>
       </c>
       <c r="U9" t="n">
-        <v>491.0520911070126</v>
+        <v>60.17</v>
       </c>
       <c r="V9" t="n">
-        <v>61.23743850120317</v>
+        <v>477.66</v>
       </c>
       <c r="W9" t="n">
-        <v>490.8270243392499</v>
+        <v>59.09</v>
       </c>
       <c r="X9" t="n">
-        <v>57.29681870299997</v>
+        <v>486.97</v>
       </c>
       <c r="Y9" t="n">
-        <v>493.0213703015323</v>
+        <v>58.43</v>
       </c>
       <c r="Z9" t="n">
-        <v>55.34071566570723</v>
+        <v>490.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>59.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>486.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>57.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>491.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>61.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>490.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>57.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>493.02</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>55.34</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>500.7</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>500.0833333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>500.2</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>501.42</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>502.1583333333334</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>502.25</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>501.98125</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>501.7777777777778</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>501.375</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>72.56969064285724</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>64.78587594701659</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>77.39676995844206</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>76.95468536742905</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>77.14952968460375</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>75.02296077106756</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>75.08132856068477</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>73.68563523174767</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>73.79101825425639</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>363</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>363</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>363</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>363</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>363</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>363</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>363</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>363</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>363</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>1</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.9090909090909091</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>493.02</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>55.34</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>500</v>
       </c>
       <c r="C10" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D10" t="n">
         <v>41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E10" t="n">
         <v>500</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>499.2185041086919</v>
-      </c>
-      <c r="J10" t="n">
-        <v>47.8434960614447</v>
-      </c>
-      <c r="K10" t="n">
-        <v>494.6099921697958</v>
-      </c>
-      <c r="L10" t="n">
-        <v>51.70528296803027</v>
-      </c>
-      <c r="M10" t="n">
-        <v>499.1147103161868</v>
-      </c>
-      <c r="N10" t="n">
-        <v>54.01192983557834</v>
-      </c>
-      <c r="O10" t="n">
-        <v>504.862811198463</v>
-      </c>
-      <c r="P10" t="n">
-        <v>53.47333769234012</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>506.2831611652968</v>
-      </c>
       <c r="R10" t="n">
-        <v>50.97579365866942</v>
+        <v>499.22</v>
       </c>
       <c r="S10" t="n">
-        <v>510.429971367548</v>
+        <v>47.84</v>
       </c>
       <c r="T10" t="n">
-        <v>50.48374562462381</v>
+        <v>494.61</v>
       </c>
       <c r="U10" t="n">
-        <v>507.2497646732052</v>
+        <v>51.71</v>
       </c>
       <c r="V10" t="n">
-        <v>51.37909101633041</v>
+        <v>499.11</v>
       </c>
       <c r="W10" t="n">
-        <v>498.6855656955216</v>
+        <v>54.01</v>
       </c>
       <c r="X10" t="n">
-        <v>56.21006418214491</v>
+        <v>504.86</v>
       </c>
       <c r="Y10" t="n">
-        <v>498.7946365451528</v>
+        <v>53.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>55.52401872475001</v>
+        <v>506.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>50.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>510.43</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>50.48</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>507.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>51.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>498.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>56.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>498.79</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>55.52</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>499.5</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>499.5</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>499.1375</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>499.33</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>499.5083333333333</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>499.3857142857143</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>499.41875</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>499.9111111111111</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>499.845</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>77.07334169477797</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>70.58718013917259</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>67.56399628315366</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>65.49474101025211</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>63.52230524696729</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>61.16203137267967</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>58.95278533231063</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>57.98632874210656</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>57.70052837713014</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>361</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>361</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>361</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>361</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>361</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>361</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>361</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>361</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>361</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.625</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.5277777777777778</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.4782608695652174</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.5531914893617021</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.6170212765957447</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.6808510638297872</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.74</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>498.79</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>55.52</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>500</v>
       </c>
       <c r="C11" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D11" t="n">
         <v>38</v>
-      </c>
-      <c r="D11" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E11" t="n">
         <v>500</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>505.745620686262</v>
-      </c>
-      <c r="J11" t="n">
-        <v>70.76542130459411</v>
-      </c>
-      <c r="K11" t="n">
-        <v>493.3215460246955</v>
-      </c>
-      <c r="L11" t="n">
-        <v>59.43337698704757</v>
-      </c>
-      <c r="M11" t="n">
-        <v>495.2449082345393</v>
-      </c>
-      <c r="N11" t="n">
-        <v>67.77105874044518</v>
-      </c>
-      <c r="O11" t="n">
-        <v>498.7715468674907</v>
-      </c>
-      <c r="P11" t="n">
-        <v>66.61549424033994</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>502.8867285866792</v>
-      </c>
       <c r="R11" t="n">
-        <v>61.86518788805799</v>
+        <v>505.75</v>
       </c>
       <c r="S11" t="n">
-        <v>502.6888531869821</v>
+        <v>70.77</v>
       </c>
       <c r="T11" t="n">
-        <v>61.88637459662623</v>
+        <v>493.32</v>
       </c>
       <c r="U11" t="n">
-        <v>499.2075542096185</v>
+        <v>59.43</v>
       </c>
       <c r="V11" t="n">
-        <v>60.37609532127227</v>
+        <v>495.24</v>
       </c>
       <c r="W11" t="n">
-        <v>498.6136387819413</v>
+        <v>67.77</v>
       </c>
       <c r="X11" t="n">
-        <v>58.61177482193968</v>
+        <v>498.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>501.5342826536513</v>
+        <v>66.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>58.61128369629125</v>
+        <v>502.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>61.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>502.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>61.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>499.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>60.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>498.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>58.61</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>501.53</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>58.61</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>496.375</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>497.8</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>498.5625</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>498.15</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>497.6916666666667</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>500.3071428571429</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>498.78125</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>499.7111111111111</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>500.02</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>79.39322625388138</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>75.62799305371877</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>73.31760425539012</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>74.37491176465355</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>69.1363141232996</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>66.4715724876401</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>65.58731507263809</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>64.32560306655931</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>63.5242441907025</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>318</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>318</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>318</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>318</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>318</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>318</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>318</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>318</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>318</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>640</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>640</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>640</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>640</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>640</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>640</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>640</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>640</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>640</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.7352941176470589</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>501.53</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>58.61</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>498</v>
       </c>
       <c r="C12" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D12" t="n">
         <v>41</v>
-      </c>
-      <c r="D12" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E12" t="n">
         <v>498</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>485.5883063454731</v>
-      </c>
-      <c r="J12" t="n">
-        <v>48.48542344516216</v>
-      </c>
-      <c r="K12" t="n">
-        <v>491.9214129348867</v>
-      </c>
-      <c r="L12" t="n">
-        <v>48.48439345480249</v>
-      </c>
-      <c r="M12" t="n">
-        <v>485.8098630884757</v>
-      </c>
-      <c r="N12" t="n">
-        <v>42.16857781141766</v>
-      </c>
-      <c r="O12" t="n">
-        <v>485.1635852649966</v>
-      </c>
-      <c r="P12" t="n">
-        <v>40.59361140385115</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>487.2343007710735</v>
-      </c>
       <c r="R12" t="n">
-        <v>40.03054112662952</v>
+        <v>485.59</v>
       </c>
       <c r="S12" t="n">
-        <v>488.9796496503909</v>
+        <v>48.49</v>
       </c>
       <c r="T12" t="n">
-        <v>44.9210025623347</v>
+        <v>491.92</v>
       </c>
       <c r="U12" t="n">
-        <v>496.404304993109</v>
+        <v>48.48</v>
       </c>
       <c r="V12" t="n">
-        <v>44.2836463261143</v>
+        <v>485.81</v>
       </c>
       <c r="W12" t="n">
-        <v>497.2472957098988</v>
+        <v>42.17</v>
       </c>
       <c r="X12" t="n">
-        <v>43.65566002472539</v>
+        <v>485.16</v>
       </c>
       <c r="Y12" t="n">
-        <v>499.1095003589868</v>
+        <v>40.59</v>
       </c>
       <c r="Z12" t="n">
-        <v>42.76584489324494</v>
+        <v>487.23</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>40.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>488.98</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>44.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>496.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>44.28</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>497.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>43.66</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>499.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>42.77</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>501.525</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>501.3333333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>501.0375</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>500.59</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>500.05</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>499.3928571428572</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>500.56875</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>500.6944444444445</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>501</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>76.47940490746512</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>68.86113240105449</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>62.87893998589671</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>59.01628504065636</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>58.93101192637597</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>63.78420050995291</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>61.72738673747254</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>59.20680302711301</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>58.10404460964831</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>362</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>362</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>362</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>362</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>362</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>362</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>362</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>362</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>362</v>
       </c>
-      <c r="BK12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>669</v>
-      </c>
       <c r="BT12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.8148148148148148</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>499.11</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>42.77</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>498</v>
       </c>
       <c r="C13" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E13" t="n">
         <v>498</v>
@@ -3558,720 +3976,819 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>489.4265746560159</v>
-      </c>
-      <c r="J13" t="n">
-        <v>27.59065370644904</v>
-      </c>
-      <c r="K13" t="n">
-        <v>484.3650888001822</v>
-      </c>
-      <c r="L13" t="n">
-        <v>38.58981210758201</v>
-      </c>
-      <c r="M13" t="n">
-        <v>486.3413290896165</v>
-      </c>
-      <c r="N13" t="n">
-        <v>40.0171868392746</v>
-      </c>
-      <c r="O13" t="n">
-        <v>486.0845113295069</v>
-      </c>
-      <c r="P13" t="n">
-        <v>37.80996912091164</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>490.7109952982283</v>
-      </c>
       <c r="R13" t="n">
-        <v>37.78747774779129</v>
+        <v>489.43</v>
       </c>
       <c r="S13" t="n">
-        <v>492.4668775933408</v>
+        <v>27.59</v>
       </c>
       <c r="T13" t="n">
-        <v>39.67319803179242</v>
+        <v>484.37</v>
       </c>
       <c r="U13" t="n">
-        <v>492.095535348714</v>
+        <v>38.59</v>
       </c>
       <c r="V13" t="n">
-        <v>40.17005527061996</v>
+        <v>486.34</v>
       </c>
       <c r="W13" t="n">
-        <v>493.2126290039405</v>
+        <v>40.02</v>
       </c>
       <c r="X13" t="n">
-        <v>39.61272848520599</v>
+        <v>486.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>495.9419277412056</v>
+        <v>37.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>40.78484960869928</v>
+        <v>490.71</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>37.79</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>492.47</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>39.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>492.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>40.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>493.21</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>39.61</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>495.94</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>40.78</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>500.05</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>500.7666666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>500.6375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>499.55</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>498.2333333333333</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>497.6428571428572</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>498.80625</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>499.0388888888889</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>499.17</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>56.9069196144019</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>52.08114395398353</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>58.82882876405071</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>57.73393716004478</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>55.00814081166128</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>54.49758466844083</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>53.5943673433832</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>53.06980349699702</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>52.20039367667643</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>387</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>387</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>387</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>387</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>387</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>387</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>387</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>387</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>387</v>
       </c>
-      <c r="BK13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>669</v>
-      </c>
       <c r="BT13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.95</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.9583333333333334</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>495.94</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>40.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G5_501_42_REL1</t>
+          <t>S13_G5_500_41_REL1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D14" t="n">
-        <v>62.26834692364714</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>539.3706059066901</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41.25152245134684</v>
-      </c>
-      <c r="K14" t="n">
-        <v>513.3867779895156</v>
-      </c>
-      <c r="L14" t="n">
-        <v>55.01222116627198</v>
-      </c>
-      <c r="M14" t="n">
-        <v>509.9759583370925</v>
-      </c>
-      <c r="N14" t="n">
-        <v>48.61408793361905</v>
-      </c>
-      <c r="O14" t="n">
-        <v>505.6386733109232</v>
-      </c>
-      <c r="P14" t="n">
-        <v>57.38045290859071</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>506.4023921410985</v>
-      </c>
       <c r="R14" t="n">
-        <v>57.10754483631457</v>
+        <v>482.24</v>
       </c>
       <c r="S14" t="n">
-        <v>503.5551441651282</v>
+        <v>67.14</v>
       </c>
       <c r="T14" t="n">
-        <v>55.63341437339844</v>
+        <v>482.27</v>
       </c>
       <c r="U14" t="n">
-        <v>502.9034540451947</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>53.07987206462047</v>
+        <v>487.42</v>
       </c>
       <c r="W14" t="n">
-        <v>498.6840129223937</v>
+        <v>62.35</v>
       </c>
       <c r="X14" t="n">
-        <v>55.53880500157873</v>
+        <v>490.34</v>
       </c>
       <c r="Y14" t="n">
-        <v>499.5940078424825</v>
+        <v>61.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>53.83306900689041</v>
+        <v>492.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>64.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>495.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>61.66</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>498.01</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>62.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>499.98</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>66.81</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>502.81</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>63.38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>499.725</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>500.7833333333334</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>500.975</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>500.81</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>502.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>501.7285714285715</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>501.45</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>501.6444444444444</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>500.955</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>69.28996590416249</v>
+        <v>501.425</v>
       </c>
       <c r="AT14" t="n">
-        <v>64.29362116277339</v>
+        <v>500.65</v>
       </c>
       <c r="AU14" t="n">
-        <v>60.81015026292897</v>
+        <v>500.7125</v>
       </c>
       <c r="AV14" t="n">
-        <v>61.36981261173933</v>
+        <v>500.52</v>
       </c>
       <c r="AW14" t="n">
-        <v>63.68181320701644</v>
+        <v>500.575</v>
       </c>
       <c r="AX14" t="n">
-        <v>65.37057473218609</v>
+        <v>500.1928571428571</v>
       </c>
       <c r="AY14" t="n">
-        <v>62.46266885108256</v>
+        <v>500.15</v>
       </c>
       <c r="AZ14" t="n">
-        <v>63.19041965205223</v>
+        <v>500.2111111111111</v>
       </c>
       <c r="BA14" t="n">
-        <v>60.84153988024958</v>
+        <v>499.99</v>
       </c>
       <c r="BB14" t="n">
-        <v>370</v>
+        <v>91.13201619079872</v>
       </c>
       <c r="BC14" t="n">
-        <v>370</v>
+        <v>83.49008424158323</v>
       </c>
       <c r="BD14" t="n">
-        <v>370</v>
+        <v>82.45441069918577</v>
       </c>
       <c r="BE14" t="n">
-        <v>370</v>
+        <v>78.83545902701398</v>
       </c>
       <c r="BF14" t="n">
-        <v>370</v>
+        <v>76.4648789205432</v>
       </c>
       <c r="BG14" t="n">
-        <v>370</v>
+        <v>74.10233237399014</v>
       </c>
       <c r="BH14" t="n">
-        <v>370</v>
+        <v>72.38034954322892</v>
       </c>
       <c r="BI14" t="n">
-        <v>370</v>
+        <v>71.3091850783839</v>
       </c>
       <c r="BJ14" t="n">
-        <v>370</v>
+        <v>71.37989843086078</v>
       </c>
       <c r="BK14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BL14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BM14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BN14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BO14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BP14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BQ14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BR14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BS14" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.8571428571428571</v>
+        <v>675</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.5833333333333334</v>
+        <v>675</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.5862068965517241</v>
+        <v>675</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.6896551724137931</v>
+        <v>675</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.7241379310344828</v>
+        <v>675</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.7241379310344828</v>
+        <v>675</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.7241379310344828</v>
+        <v>675</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.7241379310344828</v>
+        <v>675</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7931034482758621</v>
+        <v>675</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>502.81</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>63.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S13_G5_500_41_REL1</t>
+          <t>S14_G5_501_42_REL1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D15" t="n">
-        <v>60.78576723498888</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>482.2388661085257</v>
-      </c>
-      <c r="J15" t="n">
-        <v>67.14110957040209</v>
-      </c>
-      <c r="K15" t="n">
-        <v>482.2707265872</v>
-      </c>
-      <c r="L15" t="n">
-        <v>80.92753868758101</v>
-      </c>
-      <c r="M15" t="n">
-        <v>487.4186549698957</v>
-      </c>
-      <c r="N15" t="n">
-        <v>62.34739786111399</v>
-      </c>
-      <c r="O15" t="n">
-        <v>490.3391052378306</v>
-      </c>
-      <c r="P15" t="n">
-        <v>61.0529725205911</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>492.2934347974631</v>
-      </c>
       <c r="R15" t="n">
-        <v>64.5787197721754</v>
+        <v>539.37</v>
       </c>
       <c r="S15" t="n">
-        <v>495.4871154949348</v>
+        <v>41.25</v>
       </c>
       <c r="T15" t="n">
-        <v>61.65952553446709</v>
+        <v>513.39</v>
       </c>
       <c r="U15" t="n">
-        <v>498.0149892618566</v>
+        <v>55.01</v>
       </c>
       <c r="V15" t="n">
-        <v>62.1064938401457</v>
+        <v>509.98</v>
       </c>
       <c r="W15" t="n">
-        <v>499.9807682705141</v>
+        <v>48.61</v>
       </c>
       <c r="X15" t="n">
-        <v>66.80673207806925</v>
+        <v>505.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>502.8123426989752</v>
+        <v>57.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>63.3815274635071</v>
+        <v>506.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>57.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>55.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>502.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>53.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>498.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>55.54</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>499.59</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>53.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>501.425</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>500.65</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>500.7125</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>500.52</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>500.575</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>500.1928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>500.15</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>500.2111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>499.99</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>91.13201619079872</v>
+        <v>499.725</v>
       </c>
       <c r="AT15" t="n">
-        <v>83.49008424158323</v>
+        <v>500.7833333333334</v>
       </c>
       <c r="AU15" t="n">
-        <v>82.45441069918577</v>
+        <v>500.975</v>
       </c>
       <c r="AV15" t="n">
-        <v>78.83545902701398</v>
+        <v>500.81</v>
       </c>
       <c r="AW15" t="n">
-        <v>76.4648789205432</v>
+        <v>502.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>74.10233237399014</v>
+        <v>501.7285714285715</v>
       </c>
       <c r="AY15" t="n">
-        <v>72.38034954322892</v>
+        <v>501.45</v>
       </c>
       <c r="AZ15" t="n">
-        <v>71.3091850783839</v>
+        <v>501.6444444444444</v>
       </c>
       <c r="BA15" t="n">
-        <v>71.37989843086078</v>
+        <v>500.955</v>
       </c>
       <c r="BB15" t="n">
-        <v>345</v>
+        <v>69.28996590416249</v>
       </c>
       <c r="BC15" t="n">
-        <v>345</v>
+        <v>64.29362116277339</v>
       </c>
       <c r="BD15" t="n">
-        <v>345</v>
+        <v>60.81015026292897</v>
       </c>
       <c r="BE15" t="n">
-        <v>345</v>
+        <v>61.36981261173933</v>
       </c>
       <c r="BF15" t="n">
-        <v>345</v>
+        <v>63.68181320701644</v>
       </c>
       <c r="BG15" t="n">
-        <v>345</v>
+        <v>65.37057473218609</v>
       </c>
       <c r="BH15" t="n">
-        <v>345</v>
+        <v>62.46266885108256</v>
       </c>
       <c r="BI15" t="n">
-        <v>345</v>
+        <v>63.19041965205223</v>
       </c>
       <c r="BJ15" t="n">
-        <v>345</v>
+        <v>60.84153988024958</v>
       </c>
       <c r="BK15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BL15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BM15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BN15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BO15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BP15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BQ15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BR15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BS15" t="n">
-        <v>675</v>
+        <v>370</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.3333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9166666666666666</v>
+        <v>669</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.9696969696969697</v>
+        <v>669</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.9722222222222222</v>
+        <v>669</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.9090909090909091</v>
+        <v>669</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.9387755102040817</v>
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>499.59</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>53.83</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>498</v>
       </c>
       <c r="C16" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D16" t="n">
         <v>42</v>
-      </c>
-      <c r="D16" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E16" t="n">
         <v>498</v>
@@ -4296,720 +4813,819 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>474.5106996591293</v>
-      </c>
-      <c r="J16" t="n">
-        <v>46.91849908275105</v>
-      </c>
-      <c r="K16" t="n">
-        <v>492.217757865405</v>
-      </c>
-      <c r="L16" t="n">
-        <v>51.077134191911</v>
-      </c>
-      <c r="M16" t="n">
-        <v>497.705731934599</v>
-      </c>
-      <c r="N16" t="n">
-        <v>49.72497477255654</v>
-      </c>
-      <c r="O16" t="n">
-        <v>492.1029126704597</v>
-      </c>
-      <c r="P16" t="n">
-        <v>44.8940408962921</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>496.0262355543197</v>
-      </c>
       <c r="R16" t="n">
-        <v>44.18484443141686</v>
+        <v>474.51</v>
       </c>
       <c r="S16" t="n">
-        <v>496.2170183089478</v>
+        <v>46.92</v>
       </c>
       <c r="T16" t="n">
-        <v>44.22306103052215</v>
+        <v>492.22</v>
       </c>
       <c r="U16" t="n">
-        <v>502.5679650391723</v>
+        <v>51.08</v>
       </c>
       <c r="V16" t="n">
-        <v>45.89792975598254</v>
+        <v>497.71</v>
       </c>
       <c r="W16" t="n">
-        <v>501.0698004610616</v>
+        <v>49.72</v>
       </c>
       <c r="X16" t="n">
-        <v>47.88863875833401</v>
+        <v>492.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>501.2086603543052</v>
+        <v>44.89</v>
       </c>
       <c r="Z16" t="n">
-        <v>45.50116343977227</v>
+        <v>496.03</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>44.18</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>496.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>44.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>502.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>45.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>501.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>47.89</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>501.21</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>503.5</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>502.2833333333334</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>501.7125</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>501.97</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>500.2</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>499.7071428571429</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>498.94375</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>499.0277777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>498.295</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>67.27183660344052</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>63.54029998530243</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>59.60499009101503</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>56.24739193953796</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>53.71818438232378</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>52.28800687791902</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>52.83112800175196</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>53.10560030684727</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>53.01648776559986</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>398</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>398</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>398</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>398</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>398</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>398</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>398</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>398</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>398</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>1</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.7741935483870968</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>501.21</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>45.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G5_502_40_REL1</t>
+          <t>S16_G5_501_38_REL1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D17" t="n">
-        <v>59.30318754633062</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>502.054609923923</v>
-      </c>
-      <c r="J17" t="n">
-        <v>35.87963072913033</v>
-      </c>
-      <c r="K17" t="n">
-        <v>500.9581269725836</v>
-      </c>
-      <c r="L17" t="n">
-        <v>43.65600959685907</v>
-      </c>
-      <c r="M17" t="n">
-        <v>503.5277767062511</v>
-      </c>
-      <c r="N17" t="n">
-        <v>52.8996826489677</v>
-      </c>
-      <c r="O17" t="n">
-        <v>500.5542081214903</v>
-      </c>
-      <c r="P17" t="n">
-        <v>46.94829571813598</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>502.3862336075289</v>
-      </c>
       <c r="R17" t="n">
-        <v>52.05370396098759</v>
+        <v>498.58</v>
       </c>
       <c r="S17" t="n">
-        <v>503.9950463673235</v>
+        <v>49.09</v>
       </c>
       <c r="T17" t="n">
-        <v>52.65778582216346</v>
+        <v>500.22</v>
       </c>
       <c r="U17" t="n">
-        <v>503.5925633195759</v>
+        <v>42.17</v>
       </c>
       <c r="V17" t="n">
-        <v>52.67349135267789</v>
+        <v>497.52</v>
       </c>
       <c r="W17" t="n">
-        <v>506.0924072677105</v>
+        <v>40.68</v>
       </c>
       <c r="X17" t="n">
-        <v>51.24292735010851</v>
+        <v>500.56</v>
       </c>
       <c r="Y17" t="n">
-        <v>501.5582783913759</v>
+        <v>37.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>49.90163816916343</v>
+        <v>498.51</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>37.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>498.81</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>40.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>497.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>39.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>499.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>43.96</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>500.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>44.19</v>
       </c>
       <c r="AJ17" t="n">
-        <v>504.125</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>502.1666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>501.175</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>500.98</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>500.6416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>500.6571428571428</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>500.70625</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>500.9333333333333</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>500.49</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>57.10481043659982</v>
+        <v>497.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>53.24257903428629</v>
+        <v>499.2666666666667</v>
       </c>
       <c r="AU17" t="n">
-        <v>58.56188500210696</v>
+        <v>499.475</v>
       </c>
       <c r="AV17" t="n">
-        <v>61.5725555747039</v>
+        <v>500.07</v>
       </c>
       <c r="AW17" t="n">
-        <v>60.84156964791607</v>
+        <v>499.6916666666667</v>
       </c>
       <c r="AX17" t="n">
-        <v>60.90094667673442</v>
+        <v>499.7785714285714</v>
       </c>
       <c r="AY17" t="n">
-        <v>60.67171879003842</v>
+        <v>500.18125</v>
       </c>
       <c r="AZ17" t="n">
-        <v>58.83617556873965</v>
+        <v>500.0944444444444</v>
       </c>
       <c r="BA17" t="n">
-        <v>57.22936221905675</v>
+        <v>499.74</v>
       </c>
       <c r="BB17" t="n">
-        <v>379</v>
+        <v>69.02687882267314</v>
       </c>
       <c r="BC17" t="n">
-        <v>379</v>
+        <v>63.07029587866401</v>
       </c>
       <c r="BD17" t="n">
-        <v>379</v>
+        <v>57.25883665426674</v>
       </c>
       <c r="BE17" t="n">
-        <v>379</v>
+        <v>53.20869383850726</v>
       </c>
       <c r="BF17" t="n">
-        <v>379</v>
+        <v>49.96395297834452</v>
       </c>
       <c r="BG17" t="n">
-        <v>379</v>
+        <v>49.16358522570235</v>
       </c>
       <c r="BH17" t="n">
-        <v>379</v>
+        <v>49.78652828263385</v>
       </c>
       <c r="BI17" t="n">
-        <v>379</v>
+        <v>49.37078502090328</v>
       </c>
       <c r="BJ17" t="n">
-        <v>379</v>
+        <v>49.232026161839</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.7647058823529411</v>
+        <v>640</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.7368421052631579</v>
+        <v>640</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.7368421052631579</v>
+        <v>640</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.8421052631578947</v>
+        <v>640</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.9473684210526315</v>
+        <v>640</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.8695652173913043</v>
+        <v>640</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.9615384615384616</v>
+        <v>640</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.896551724137931</v>
+        <v>640</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>500.14</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>44.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S16_G5_501_38_REL1</t>
+          <t>S17_G5_502_40_REL1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D18" t="n">
-        <v>56.33802816901409</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>498.5827635827789</v>
-      </c>
-      <c r="J18" t="n">
-        <v>49.09050585172702</v>
-      </c>
-      <c r="K18" t="n">
-        <v>500.2171005689743</v>
-      </c>
-      <c r="L18" t="n">
-        <v>42.17478691454988</v>
-      </c>
-      <c r="M18" t="n">
-        <v>497.5158686069374</v>
-      </c>
-      <c r="N18" t="n">
-        <v>40.68328547096383</v>
-      </c>
-      <c r="O18" t="n">
-        <v>500.5569832457326</v>
-      </c>
-      <c r="P18" t="n">
-        <v>37.36033763934114</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>498.5110243976009</v>
-      </c>
       <c r="R18" t="n">
-        <v>37.83739373988634</v>
+        <v>502.05</v>
       </c>
       <c r="S18" t="n">
-        <v>498.8092122382199</v>
+        <v>35.88</v>
       </c>
       <c r="T18" t="n">
-        <v>40.21443390102283</v>
+        <v>500.96</v>
       </c>
       <c r="U18" t="n">
-        <v>497.1414476012409</v>
+        <v>43.66</v>
       </c>
       <c r="V18" t="n">
-        <v>39.55245036812582</v>
+        <v>503.53</v>
       </c>
       <c r="W18" t="n">
-        <v>499.4164628165295</v>
+        <v>52.9</v>
       </c>
       <c r="X18" t="n">
-        <v>43.95656019583556</v>
+        <v>500.55</v>
       </c>
       <c r="Y18" t="n">
-        <v>500.1443404223155</v>
+        <v>46.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>44.1887367955237</v>
+        <v>502.39</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>52.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>52.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>503.59</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>506.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>51.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>501.56</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>49.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>497.7</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>499.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>499.475</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>500.07</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>499.6916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>499.7785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>500.18125</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>500.0944444444444</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>499.74</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>69.02687882267314</v>
+        <v>504.125</v>
       </c>
       <c r="AT18" t="n">
-        <v>63.07029587866401</v>
+        <v>502.1666666666667</v>
       </c>
       <c r="AU18" t="n">
-        <v>57.25883665426674</v>
+        <v>501.175</v>
       </c>
       <c r="AV18" t="n">
-        <v>53.20869383850726</v>
+        <v>500.98</v>
       </c>
       <c r="AW18" t="n">
-        <v>49.96395297834452</v>
+        <v>500.6416666666667</v>
       </c>
       <c r="AX18" t="n">
-        <v>49.16358522570235</v>
+        <v>500.6571428571428</v>
       </c>
       <c r="AY18" t="n">
-        <v>49.78652828263385</v>
+        <v>500.70625</v>
       </c>
       <c r="AZ18" t="n">
-        <v>49.37078502090328</v>
+        <v>500.9333333333333</v>
       </c>
       <c r="BA18" t="n">
-        <v>49.232026161839</v>
+        <v>500.49</v>
       </c>
       <c r="BB18" t="n">
-        <v>316</v>
+        <v>57.10481043659982</v>
       </c>
       <c r="BC18" t="n">
-        <v>316</v>
+        <v>53.24257903428629</v>
       </c>
       <c r="BD18" t="n">
-        <v>316</v>
+        <v>58.56188500210696</v>
       </c>
       <c r="BE18" t="n">
-        <v>316</v>
+        <v>61.5725555747039</v>
       </c>
       <c r="BF18" t="n">
-        <v>316</v>
+        <v>60.84156964791607</v>
       </c>
       <c r="BG18" t="n">
-        <v>316</v>
+        <v>60.90094667673442</v>
       </c>
       <c r="BH18" t="n">
-        <v>316</v>
+        <v>60.67171879003842</v>
       </c>
       <c r="BI18" t="n">
-        <v>316</v>
+        <v>58.83617556873965</v>
       </c>
       <c r="BJ18" t="n">
-        <v>316</v>
+        <v>57.22936221905675</v>
       </c>
       <c r="BK18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BL18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BM18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BN18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BO18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BP18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BQ18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BR18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BS18" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.5217391304347826</v>
+        <v>669</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.6086956521739131</v>
+        <v>669</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.6086956521739131</v>
+        <v>669</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.7826086956521739</v>
+        <v>669</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.7241379310344828</v>
+        <v>669</v>
       </c>
       <c r="CB18" t="n">
-        <v>0</v>
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>501.56</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>49.9</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>498</v>
       </c>
       <c r="C19" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D19" t="n">
         <v>38</v>
-      </c>
-      <c r="D19" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E19" t="n">
         <v>498</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>488.6216620865245</v>
-      </c>
-      <c r="J19" t="n">
-        <v>28.43633810837204</v>
-      </c>
-      <c r="K19" t="n">
-        <v>494.0706311298088</v>
-      </c>
-      <c r="L19" t="n">
-        <v>38.48540208630806</v>
-      </c>
-      <c r="M19" t="n">
-        <v>495.2107761128254</v>
-      </c>
-      <c r="N19" t="n">
-        <v>40.0542648984078</v>
-      </c>
-      <c r="O19" t="n">
-        <v>497.0033317052992</v>
-      </c>
-      <c r="P19" t="n">
-        <v>41.3434793324827</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>496.560584799526</v>
-      </c>
       <c r="R19" t="n">
-        <v>38.46970867305969</v>
+        <v>488.62</v>
       </c>
       <c r="S19" t="n">
-        <v>495.8892779555958</v>
+        <v>28.44</v>
       </c>
       <c r="T19" t="n">
-        <v>36.9828660107965</v>
+        <v>494.07</v>
       </c>
       <c r="U19" t="n">
-        <v>495.3346291689869</v>
+        <v>38.49</v>
       </c>
       <c r="V19" t="n">
-        <v>35.39037590538579</v>
+        <v>495.21</v>
       </c>
       <c r="W19" t="n">
-        <v>495.8697431069065</v>
+        <v>40.05</v>
       </c>
       <c r="X19" t="n">
-        <v>35.25165961973686</v>
+        <v>497</v>
       </c>
       <c r="Y19" t="n">
-        <v>494.3920217035966</v>
+        <v>41.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>34.83959586041189</v>
+        <v>496.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>38.47</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>495.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>36.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>495.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>35.39</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>495.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>35.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>494.39</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>34.84</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>505.775</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>502.85</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>502</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>502.9</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>503.0333333333334</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>502.7428571428571</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>502.28125</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>501.8333333333333</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>502.055</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>54.07239938267951</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>54.52394733814981</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>54.66854671563897</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>56.26393160809152</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>54.49494370020845</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>52.90819156514308</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>50.08295267291556</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>47.35017306081244</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>45.47660909742502</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>408</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>408</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>408</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>408</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>408</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>408</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>408</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>408</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>408</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.4210526315789473</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>1</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>1</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.9565217391304348</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>494.39</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>34.84</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D20" t="n">
         <v>40</v>
-      </c>
-      <c r="D20" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E20" t="n">
         <v>500</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>487.2607499295961</v>
-      </c>
-      <c r="J20" t="n">
-        <v>44.91161822685273</v>
-      </c>
-      <c r="K20" t="n">
-        <v>499.0962359682121</v>
-      </c>
-      <c r="L20" t="n">
-        <v>45.34074340401851</v>
-      </c>
-      <c r="M20" t="n">
-        <v>498.6127685752198</v>
-      </c>
-      <c r="N20" t="n">
-        <v>40.29117009773154</v>
-      </c>
-      <c r="O20" t="n">
-        <v>501.4229959011067</v>
-      </c>
-      <c r="P20" t="n">
-        <v>40.08686173536331</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>499.4299111639371</v>
-      </c>
       <c r="R20" t="n">
-        <v>39.16404331035916</v>
+        <v>487.26</v>
       </c>
       <c r="S20" t="n">
-        <v>497.4173968428121</v>
+        <v>44.91</v>
       </c>
       <c r="T20" t="n">
-        <v>36.1408489844338</v>
+        <v>499.1</v>
       </c>
       <c r="U20" t="n">
-        <v>499.0706197535776</v>
+        <v>45.34</v>
       </c>
       <c r="V20" t="n">
-        <v>35.23726806409224</v>
+        <v>498.61</v>
       </c>
       <c r="W20" t="n">
-        <v>497.6195510285518</v>
+        <v>40.29</v>
       </c>
       <c r="X20" t="n">
-        <v>35.13363305742219</v>
+        <v>501.42</v>
       </c>
       <c r="Y20" t="n">
-        <v>496.3928266421764</v>
+        <v>40.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>36.73053505137485</v>
+        <v>499.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>39.16</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>497.42</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>36.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>499.07</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>35.24</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>497.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>35.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>496.39</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>36.73</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>500.975</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>500.1833333333333</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>499.4125</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>499.74</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>499.7083333333333</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>500.1714285714286</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>500.14375</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>500.3111111111111</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>500.4</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>63.78890479542661</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>58.34509167206975</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>56.35084155316583</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>52.77113225997714</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>49.940196874751</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>47.10958999384048</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>45.08171010440376</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>43.78384898679838</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>42.33296587767033</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>387</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>387</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>387</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>387</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>387</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>387</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>387</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>387</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>387</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.6206896551724138</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.7</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.7</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.7</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.7</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.7666666666666667</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>496.39</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>36.73</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>502</v>
       </c>
       <c r="C21" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D21" t="n">
         <v>39</v>
-      </c>
-      <c r="D21" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E21" t="n">
         <v>502</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>518.0416618655584</v>
-      </c>
-      <c r="J21" t="n">
-        <v>53.15123490884855</v>
-      </c>
-      <c r="K21" t="n">
-        <v>515.8315478847697</v>
-      </c>
-      <c r="L21" t="n">
-        <v>55.78551291604064</v>
-      </c>
-      <c r="M21" t="n">
-        <v>511.3174222850914</v>
-      </c>
-      <c r="N21" t="n">
-        <v>52.22858592752632</v>
-      </c>
-      <c r="O21" t="n">
-        <v>501.3692330355713</v>
-      </c>
-      <c r="P21" t="n">
-        <v>53.81050632861974</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>507.1621432010062</v>
-      </c>
       <c r="R21" t="n">
-        <v>57.60855589237519</v>
+        <v>518.04</v>
       </c>
       <c r="S21" t="n">
-        <v>504.9265120536897</v>
+        <v>53.15</v>
       </c>
       <c r="T21" t="n">
-        <v>54.05029580146235</v>
+        <v>515.83</v>
       </c>
       <c r="U21" t="n">
-        <v>502.2311889990679</v>
+        <v>55.79</v>
       </c>
       <c r="V21" t="n">
-        <v>51.6366255870079</v>
+        <v>511.32</v>
       </c>
       <c r="W21" t="n">
-        <v>500.597236307291</v>
+        <v>52.23</v>
       </c>
       <c r="X21" t="n">
-        <v>51.18013066333636</v>
+        <v>501.37</v>
       </c>
       <c r="Y21" t="n">
-        <v>501.6855200794946</v>
+        <v>53.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>53.32322315420368</v>
+        <v>507.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>57.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>504.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>54.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>502.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>51.64</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>500.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>51.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>501.69</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>53.32</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>500.175</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>500.1666666666667</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>500.6625</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>501.26</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>500.15</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>499.2285714285715</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>500.5</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>500.3833333333333</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>500.26</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>83.14742554643529</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>75.30364459233623</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>68.8167755256667</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>63.6008836416602</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>67.96587992024627</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>65.32056587729942</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>64.42660552908248</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>63.62007675778666</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>63.50781369248984</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>361</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>361</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>361</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>361</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>361</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>361</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>361</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>361</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>361</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.95</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.9565217391304348</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>501.69</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>53.32</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.75</v>
       </c>
       <c r="C22" t="n">
+        <v>59.2290585618977</v>
+      </c>
+      <c r="D22" t="n">
         <v>39.95</v>
-      </c>
-      <c r="D22" t="n">
-        <v>59.2290585618977</v>
       </c>
       <c r="E22" t="n">
         <v>499.75</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5085000000000001</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>77.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.4785</v>
+      </c>
       <c r="I22" t="n">
-        <v>496.1318402591534</v>
+        <v>2.569</v>
       </c>
       <c r="J22" t="n">
-        <v>46.5413713866073</v>
+        <v>2.6175</v>
       </c>
       <c r="K22" t="n">
-        <v>496.5234874083188</v>
+        <v>2.6595</v>
       </c>
       <c r="L22" t="n">
-        <v>50.6871517834412</v>
+        <v>2.673</v>
       </c>
       <c r="M22" t="n">
-        <v>496.5247299415325</v>
+        <v>2.684</v>
       </c>
       <c r="N22" t="n">
-        <v>49.27900926330398</v>
+        <v>2.3825</v>
       </c>
       <c r="O22" t="n">
-        <v>496.5855826820989</v>
+        <v>2.258999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>48.91547684320443</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>497.5809205552092</v>
-      </c>
+        <v>2.395</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>48.79981720712719</v>
+        <v>496.1319999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>497.5138859598102</v>
+        <v>46.542</v>
       </c>
       <c r="T22" t="n">
-        <v>48.95210986529967</v>
+        <v>496.524</v>
       </c>
       <c r="U22" t="n">
-        <v>498.3563275991459</v>
+        <v>50.6875</v>
       </c>
       <c r="V22" t="n">
-        <v>48.39298728005824</v>
+        <v>496.525</v>
       </c>
       <c r="W22" t="n">
-        <v>498.4444334141837</v>
+        <v>49.278</v>
       </c>
       <c r="X22" t="n">
-        <v>49.37978156788021</v>
+        <v>496.5845</v>
       </c>
       <c r="Y22" t="n">
-        <v>498.3030174780721</v>
+        <v>48.91550000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>48.75560474296382</v>
+        <v>497.5804999999999</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>48.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>497.516</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>48.9515</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>498.3559999999999</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>48.3935</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>498.4450000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>49.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>498.3025</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>48.7555</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500.67125</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>500.6875</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>500.4037500000001</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>500.6715</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>500.687</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>500.404</v>
+      </c>
+      <c r="AV22" t="n">
         <v>500.483</v>
       </c>
-      <c r="AN22" t="n">
-        <v>500.2058333333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>500.1710714285714</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>500.1653125</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>500.1519444444444</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>500.11775</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>71.53475786019327</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>66.25090032501102</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>64.74680009838536</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>62.87450085058985</v>
-      </c>
       <c r="AW22" t="n">
-        <v>61.26255394036652</v>
+        <v>500.2054999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>59.98597443861448</v>
+        <v>500.1714999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>59.02161486612196</v>
+        <v>500.166</v>
       </c>
       <c r="AZ22" t="n">
-        <v>58.02807312163435</v>
+        <v>500.1504999999999</v>
       </c>
       <c r="BA22" t="n">
-        <v>57.65021490514363</v>
+        <v>500.1184999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>71.53449999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>66.25049999999999</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>64.74699999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>62.87349999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>61.262</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>59.985</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>59.02199999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>58.029</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>57.6495</v>
+      </c>
+      <c r="BK22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>360.25</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>659.45</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.5936997724497723</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.641696331237151</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.703941345073593</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7397779604789737</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7717549359826397</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8246177351772704</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.8247813657635366</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8370034013789327</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8039240385607265</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>498.3025</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>48.7555</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.371706582097068</v>
       </c>
       <c r="C23" t="n">
+        <v>2.176547746165718</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.468081454788778</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.176547746165718</v>
       </c>
       <c r="E23" t="n">
         <v>1.371706582097068</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01954078056944396</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.292692009559488</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.322951438422168</v>
+      </c>
       <c r="I23" t="n">
-        <v>19.32124681011533</v>
+        <v>0.3039373204080771</v>
       </c>
       <c r="J23" t="n">
-        <v>11.54399767587448</v>
+        <v>0.2448173325477375</v>
       </c>
       <c r="K23" t="n">
-        <v>12.11269624893185</v>
+        <v>0.2248385385583455</v>
       </c>
       <c r="L23" t="n">
-        <v>10.04470438624419</v>
+        <v>0.2257875107263465</v>
       </c>
       <c r="M23" t="n">
-        <v>10.31654034231226</v>
+        <v>0.2280904714316114</v>
       </c>
       <c r="N23" t="n">
-        <v>8.509284123464113</v>
+        <v>0.3038849332092313</v>
       </c>
       <c r="O23" t="n">
-        <v>7.470718875772081</v>
+        <v>0.3269620934088779</v>
       </c>
       <c r="P23" t="n">
-        <v>8.421333755100358</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7.852338640949751</v>
-      </c>
+        <v>0.3505859756404832</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>8.467483077691917</v>
+        <v>19.32119332699063</v>
       </c>
       <c r="S23" t="n">
-        <v>6.990527986193745</v>
+        <v>11.54351839094586</v>
       </c>
       <c r="T23" t="n">
-        <v>7.739656874886706</v>
+        <v>12.11324303570706</v>
       </c>
       <c r="U23" t="n">
-        <v>5.4432125318071</v>
+        <v>10.04458737461703</v>
       </c>
       <c r="V23" t="n">
-        <v>7.971520487945698</v>
+        <v>10.31698420847365</v>
       </c>
       <c r="W23" t="n">
-        <v>4.7853544870769</v>
+        <v>8.509024682807754</v>
       </c>
       <c r="X23" t="n">
-        <v>8.74063705484326</v>
+        <v>7.471373772783127</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.969452708892084</v>
+        <v>8.421867823207567</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.831430424790223</v>
+        <v>7.851765792013381</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>8.467915918335514</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>6.990387685958483</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7.740468009106426</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.443521886271402</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>7.972599308684848</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>4.785343302869268</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>8.742185683587131</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.969067071876291</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.830953074347438</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.081291968861183</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.317716378361751</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.491340685247235</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.081298897338076</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.316912873449899</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.491260152389673</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.484658741579148</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.44981623154909</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.301012732438747</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.13430993361313</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.163113881734873</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.068901889791572</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>10.5976387207874</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.989555213639646</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.947341215097334</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>7.569040319421508</v>
-      </c>
       <c r="AW23" t="n">
-        <v>7.935501969059937</v>
+        <v>1.449760325019279</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.90361789765078</v>
+        <v>1.301166581835021</v>
       </c>
       <c r="AY23" t="n">
-        <v>7.809087944473531</v>
+        <v>1.133710257238779</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7.883564621238419</v>
+        <v>1.161253746240626</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.144851951144359</v>
+        <v>1.068605953666046</v>
       </c>
       <c r="BB23" t="n">
+        <v>10.59803431376732</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8.990369979507019</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.94721076525396</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.568901940106462</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.93583849580994</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>7.90297179280647</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>7.809150233439043</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>7.884371549898071</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.144930276590852</v>
+      </c>
+      <c r="BK23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>26.65742712739981</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>20.10623103209026</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.3134328190389978</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2508623885089507</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1302911068327449</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1235082206570386</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1258255184424478</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1383399834820684</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1350297738940196</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1438806274892215</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.210999165770032</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.969067071876291</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>7.830953074347438</v>
       </c>
     </row>
   </sheetData>
